--- a/naver-place-crawler/results_health/금정구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/금정구_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="43" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>마블피트니스 헬스&amp;PT 부산대장전점</t>
+          <t>일레븐핏 부산대점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lsh20220@naver.com</t>
+          <t>elevenfit@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1416-9683</t>
+          <t>0507-1495-7982</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1719번길 47 2층</t>
+          <t>부산광역시 금정구 금강로 209 한신시티빌 B1F</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lsh20220</t>
+          <t>https://blog.naver.com/elevenfit</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="Q2" t="n">
-        <v>127</v>
+        <v>751</v>
       </c>
       <c r="R2" t="n">
-        <v>334</v>
+        <v>885</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2024917216</t>
+          <t>1356064248</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024917216</t>
+          <t>https://m.place.naver.com/place/1356064248</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>헬스스타짐 헬스&amp;PT&amp;스피닝 구서점</t>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 동래점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>healthstargym01@naver.com</t>
+          <t>resort_15@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1395-8189</t>
+          <t>0507-1487-7205</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 구서로 12 2층 헬스스타짐 구서점</t>
+          <t>부산광역시 동래구 중앙대로 1393 9-10층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthstargym01</t>
+          <t>https://blog.naver.com/resort_15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="Q3" t="n">
-        <v>141</v>
+        <v>259</v>
       </c>
       <c r="R3" t="n">
-        <v>215</v>
+        <v>427</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2086997985</t>
+          <t>2088626361</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2086997985</t>
+          <t>https://m.place.naver.com/place/2088626361</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피트니스인앤스타 헬스&amp;PT&amp;스피닝</t>
+          <t>헬스스타짐 헬스&amp;PT&amp;스피닝 구서점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>inanstarbusandae@naver.com</t>
+          <t>healthstargym01@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1366-0046</t>
+          <t>0507-1395-8189</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1685번길 7 피트니스인앤스타 2층</t>
+          <t>부산광역시 금정구 구서로 12 2층 헬스스타짐 구서점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/belief_s_im</t>
+          <t>https://blog.naver.com/healthstargym01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>787</v>
+        <v>80</v>
       </c>
       <c r="Q4" t="n">
-        <v>1306</v>
+        <v>150</v>
       </c>
       <c r="R4" t="n">
-        <v>2093</v>
+        <v>230</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +824,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1044450403</t>
+          <t>2086997985</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1044450403</t>
+          <t>https://m.place.naver.com/place/2086997985</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 구서점</t>
+          <t>포드짐 남산점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mutgym_@naver.com</t>
+          <t>fordgym2_namsan@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1483-8689</t>
+          <t>0507-1411-7637</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 두실로 5 2층</t>
+          <t>부산광역시 금정구 중앙대로 1989 302호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym_</t>
+          <t>https://www.instagram.com/fordgym_namsan</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>782</v>
+        <v>904</v>
       </c>
       <c r="Q5" t="n">
-        <v>435</v>
+        <v>248</v>
       </c>
       <c r="R5" t="n">
-        <v>1217</v>
+        <v>1152</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,56 +918,56 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1982277371</t>
+          <t>1054720258</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1982277371</t>
+          <t>https://m.place.naver.com/place/1054720258</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>오성피트니스 헬스,PT&amp;필라테스 구서점</t>
+          <t>스카이짐 24H &amp; 기구필라테스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hakunashop@naver.com</t>
+          <t>skygym99@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1458-5563</t>
+          <t>0507-1484-5661</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 528 7층, 8층 오성피트니스 구서점</t>
+          <t>부산광역시 금정구 금강로 441 7층 8층 9층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/osungfitness_guseo</t>
+          <t>http://www.skygym.co.kr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>890</v>
+        <v>2708</v>
       </c>
       <c r="Q6" t="n">
-        <v>342</v>
+        <v>118</v>
       </c>
       <c r="R6" t="n">
-        <v>1232</v>
+        <v>2826</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1012,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1131532901</t>
+          <t>1730198934</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131532901</t>
+          <t>https://m.place.naver.com/place/1730198934</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>플러스짐 / 플러스휘트니스 헬스&amp;PT 서동점</t>
+          <t>마블피트니스 헬스&amp;PT 부산대장전점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>wntjdgh07@naver.com</t>
+          <t>lsh20220@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>051-711-1234</t>
+          <t>0507-1416-9683</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 서동로175번길 30 재원빌딩 2층,3층</t>
+          <t>부산광역시 금정구 중앙대로1719번길 47 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wntjdgh07</t>
+          <t>https://blog.naver.com/lsh20220</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>134</v>
+        <v>217</v>
       </c>
       <c r="Q7" t="n">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="R7" t="n">
-        <v>192</v>
+        <v>370</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1903154613</t>
+          <t>2024917216</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1903154613</t>
+          <t>https://m.place.naver.com/place/2024917216</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>허그짐 구서점 헬스&amp;PT</t>
+          <t>라이트짐 헬스&amp;PT 장전점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>huggym_guseo@naver.com</t>
+          <t>weejae0420@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1316-7789</t>
+          <t>0507-1361-2316</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 503 롯데캐슬상가 4층</t>
+          <t>부산광역시 금정구 중앙대로1719번길 23 우남빌딩 6층 601호 라이트짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/huggym_guseo</t>
+          <t>https://www.instagram.com/rightgym_pnu</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>120</v>
+        <v>739</v>
       </c>
       <c r="Q8" t="n">
-        <v>90</v>
+        <v>285</v>
       </c>
       <c r="R8" t="n">
-        <v>210</v>
+        <v>1024</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,24 +1200,24 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2015222427</t>
+          <t>1184810796</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2015222427</t>
+          <t>https://m.place.naver.com/place/1184810796</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠센터</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q9" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R9" t="n">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1308,41 +1308,41 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>라이트짐 장전역점</t>
+          <t>핏핏바디트레이닝 PT센터 구서점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bderpccis@naver.com</t>
+          <t>fitfitness@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1361-2316</t>
+          <t>051-512-5818</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1719번길 23 우남빌딩 6층 601호 라이트짐</t>
+          <t>부산광역시 금정구 중앙대로1873번길 14 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rightgym_pnu</t>
+          <t>https://blog.naver.com/fitfitness</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>725</v>
+        <v>212</v>
       </c>
       <c r="Q10" t="n">
-        <v>276</v>
+        <v>193</v>
       </c>
       <c r="R10" t="n">
-        <v>1001</v>
+        <v>405</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,61 +1392,61 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1184810796</t>
+          <t>38642628</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1184810796</t>
+          <t>https://m.place.naver.com/place/38642628</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>모션업PT 온천장점</t>
+          <t>핏핏바디트레이닝 PT센터 금정본점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rehab_coach@naver.com</t>
+          <t>fitfitness@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1488-3306</t>
+          <t>051-512-5868</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 온천장로 136-1 6층 모션업PT</t>
+          <t>부산광역시 금정구 금샘로 387-1 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/765659</t>
+          <t>https://blog.naver.com/fitfitness</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>160</v>
+        <v>214</v>
       </c>
       <c r="Q11" t="n">
-        <v>470</v>
+        <v>313</v>
       </c>
       <c r="R11" t="n">
-        <v>630</v>
+        <v>527</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,953 +1486,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1670613112</t>
+          <t>37302400</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1670613112</t>
+          <t>https://m.place.naver.com/place/37302400</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>비너스짐</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>iamjollykim@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1464-6250</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>부산광역시 금정구 부산대학로 31 3,4층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/venusgym.busan</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>199</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>205</v>
-      </c>
-      <c r="R12" t="n">
-        <v>404</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1858723770</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1858723770</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>일레븐핏 부산대점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>elevenfit@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1495-7982</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>부산광역시 금정구 금강로 209 한신시티빌 B1F</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/elevenfit</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>134</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>749</v>
-      </c>
-      <c r="R13" t="n">
-        <v>883</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1356064248</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1356064248</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>위드피트니스 &amp; PT 부산대점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>withfitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1397-4887</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>부산광역시 금정구 부산대학로 10 대우아파트 상가 위드피트니스 헬스장</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/withfitness</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1164</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1687</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2851</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>13415160</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/13415160</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>포드짐 남산점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>fordgym2_namsan@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1411-7637</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>부산광역시 금정구 중앙대로 1989 302호</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/fordgym_namsan</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>897</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>246</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1143</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1054720258</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1054720258</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>레고핏 피트니스 구서점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>luvrover99@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>부산광역시 금정구 중앙대로1929번길 11 유림빌딩 2층</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/luvrover99</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>295</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>305</v>
-      </c>
-      <c r="R16" t="n">
-        <v>600</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1940991515</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1940991515</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>스카이짐 24H &amp; 기구필라테스</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>skygym99@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1484-5661</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>부산광역시 금정구 금강로 441 7층 8층 9층</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>http://www.skygym.co.kr</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>2704</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>115</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2819</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1730198934</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1730198934</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>워너짐 부산대</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>wannagym87@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1313-1519</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>부산광역시 금정구 금강로 252-1 지하1층</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/wannagym9_busanuni</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>586</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>33</v>
-      </c>
-      <c r="R18" t="n">
-        <v>619</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1046756058</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1046756058</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>더매력짐&amp;기구필라테스</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>tmrgym1716@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1419-6678</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>부산광역시 금정구 부곡로 50</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/tmrgym1716</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>189</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>551</v>
-      </c>
-      <c r="R19" t="n">
-        <v>740</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1639193921</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1639193921</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>죠짐크로스핏</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>sanjuk001@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1348-4870</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>부산광역시 금정구 금강로 252-1 1층</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/jogym_jiiiinak/</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>86</v>
-      </c>
-      <c r="R20" t="n">
-        <v>92</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>36604868</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/36604868</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>무지개휘트니스 남산점PT&amp;필라테스&amp;요가&amp;줌바</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>rainbow4441@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1442-4445</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>부산광역시 금정구 금강로 700 남산빌딩 4층 무지개휘트니스</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/rainbow4441</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>886</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>876</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1762</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>381975477</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/381975477</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/금정구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/금정구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일레븐핏 부산대점</t>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 동래점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>elevenfit@naver.com</t>
+          <t>resort_15@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1495-7982</t>
+          <t>0507-1487-7205</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 209 한신시티빌 B1F</t>
+          <t>부산광역시 동래구 중앙대로 1393 9-10층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/elevenfit</t>
+          <t>https://blog.naver.com/resort_15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="Q2" t="n">
-        <v>751</v>
+        <v>264</v>
       </c>
       <c r="R2" t="n">
-        <v>885</v>
+        <v>432</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1356064248</t>
+          <t>2088626361</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1356064248</t>
+          <t>https://m.place.naver.com/place/2088626361</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 동래점</t>
+          <t>헬스스타짐 헬스&amp;PT&amp;스피닝 구서점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>resort_15@naver.com</t>
+          <t>healthstargym01@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1487-7205</t>
+          <t>0507-1395-8189</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 중앙대로 1393 9-10층</t>
+          <t>부산 금정구 구서로 12 2층 헬스스타짐 구서점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_15</t>
+          <t>https://blog.naver.com/healthstargym01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="Q3" t="n">
-        <v>259</v>
+        <v>151</v>
       </c>
       <c r="R3" t="n">
-        <v>427</v>
+        <v>231</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2088626361</t>
+          <t>2086997985</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2088626361</t>
+          <t>https://m.place.naver.com/place/2086997985</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>헬스스타짐 헬스&amp;PT&amp;스피닝 구서점</t>
+          <t>윤피티앤짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>healthstargym01@naver.com</t>
+          <t>yunpt-gym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1395-8189</t>
+          <t>0507-1391-9943</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 구서로 12 2층 헬스스타짐 구서점</t>
+          <t>부산 금정구 부산대학로49번길 33-3 1층 좌측</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthstargym01</t>
+          <t>https://blog.naver.com/yunpt-gym</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -794,10 +794,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wpgkdoj</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="Q4" t="n">
-        <v>150</v>
+        <v>43</v>
       </c>
       <c r="R4" t="n">
-        <v>230</v>
+        <v>93</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2086997985</t>
+          <t>1010289296</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2086997985</t>
+          <t>https://m.place.naver.com/place/1010289296</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,29 +850,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>포드짐 남산점</t>
+          <t>레고핏 피트니스 구서점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fordgym2_namsan@naver.com</t>
+          <t>luvrover99@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1411-7637</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로 1989 302호</t>
+          <t>부산 금정구 중앙대로1929번길 11 유림빌딩 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fordgym_namsan</t>
+          <t>https://blog.naver.com/luvrover99</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,15 +883,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4hp5y</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>904</v>
+        <v>300</v>
       </c>
       <c r="Q5" t="n">
-        <v>248</v>
+        <v>308</v>
       </c>
       <c r="R5" t="n">
-        <v>1152</v>
+        <v>608</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1054720258</t>
+          <t>1940991515</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054720258</t>
+          <t>https://m.place.naver.com/place/1940991515</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,34 +944,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스카이짐 24H &amp; 기구필라테스</t>
+          <t>마블피트니스 헬스&amp;PT 부산대장전점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>skygym99@naver.com</t>
+          <t>lsh20220@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1484-5661</t>
+          <t>0507-1416-9683</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 441 7층 8층 9층</t>
+          <t>부산광역시 금정구 중앙대로1719번길 47 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.skygym.co.kr</t>
+          <t>https://blog.naver.com/lsh20220</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -993,17 +997,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2708</v>
+        <v>223</v>
       </c>
       <c r="Q6" t="n">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="R6" t="n">
-        <v>2826</v>
+        <v>379</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1730198934</t>
+          <t>2024917216</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1730198934</t>
+          <t>https://m.place.naver.com/place/2024917216</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마블피트니스 헬스&amp;PT 부산대장전점</t>
+          <t>일레븐핏 부산대점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lsh20220@naver.com</t>
+          <t>elevenfit@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1416-9683</t>
+          <t>0507-1495-7982</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1719번길 47 2층</t>
+          <t>부산광역시 금정구 금강로 209 한신시티빌 B1F</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lsh20220</t>
+          <t>https://blog.naver.com/elevenfit</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>217</v>
+        <v>134</v>
       </c>
       <c r="Q7" t="n">
-        <v>153</v>
+        <v>751</v>
       </c>
       <c r="R7" t="n">
-        <v>370</v>
+        <v>885</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,56 +1110,56 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2024917216</t>
+          <t>1356064248</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024917216</t>
+          <t>https://m.place.naver.com/place/1356064248</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>라이트짐 헬스&amp;PT 장전점</t>
+          <t>스카이짐 24H &amp; 기구필라테스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>weejae0420@naver.com</t>
+          <t>skygym99@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1361-2316</t>
+          <t>0507-1484-5661</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1719번길 23 우남빌딩 6층 601호 라이트짐</t>
+          <t>부산광역시 금정구 금강로 441 7층 8층 9층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rightgym_pnu</t>
+          <t>http://www.skygym.co.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,7 +1169,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1181,17 +1185,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>739</v>
+        <v>2709</v>
       </c>
       <c r="Q8" t="n">
-        <v>285</v>
+        <v>118</v>
       </c>
       <c r="R8" t="n">
-        <v>1024</v>
+        <v>2827</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,78 +1204,78 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1184810796</t>
+          <t>1730198934</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1184810796</t>
+          <t>https://m.place.naver.com/place/1730198934</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠센터</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>승산스포렉스</t>
+          <t>포드짐 남산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>seungsan_sporex@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>spok7560@daum.net</t>
-        </is>
-      </c>
+          <t>fordgym2_namsan@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1359-6016</t>
+          <t>0507-1411-7637</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 구서중앙로15번길 20</t>
+          <t>부산 금정구 중앙대로 1989 302호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://www.sspo.co.kr</t>
+          <t>https://www.instagram.com/fordgym_namsan</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wao4ubg</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>323</v>
+        <v>904</v>
       </c>
       <c r="Q9" t="n">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="R9" t="n">
-        <v>561</v>
+        <v>1153</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,17 +1302,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>37915700</t>
+          <t>1054720258</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37915700</t>
+          <t>https://m.place.naver.com/place/1054720258</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1320,29 +1324,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>핏핏바디트레이닝 PT센터 구서점</t>
+          <t>라이트짐 헬스&amp;PT 장전점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fitfitness@naver.com</t>
+          <t>weejae0420@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>051-512-5818</t>
+          <t>0507-1361-2316</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1873번길 14 3층</t>
+          <t>부산 금정구 중앙대로1719번길 23 우남빌딩 6층 601호 라이트짐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitfitness</t>
+          <t>https://www.instagram.com/rightgym_pnu</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,15 +1361,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45b6h</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,13 +1385,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>212</v>
+        <v>739</v>
       </c>
       <c r="Q10" t="n">
-        <v>193</v>
+        <v>286</v>
       </c>
       <c r="R10" t="n">
-        <v>405</v>
+        <v>1025</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,51 +1400,55 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>38642628</t>
+          <t>1184810796</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38642628</t>
+          <t>https://m.place.naver.com/place/1184810796</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠센터</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>핏핏바디트레이닝 PT센터 금정본점</t>
+          <t>승산스포렉스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fitfitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>seungsan_sporex@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>spok7560@daum.net</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>051-512-5868</t>
+          <t>0507-1359-6016</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금샘로 387-1 2층</t>
+          <t>부산광역시 금정구 구서중앙로15번길 20</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitfitness</t>
+          <t>http://www.sspo.co.kr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1471,32 +1483,220 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>323</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>239</v>
+      </c>
+      <c r="R11" t="n">
+        <v>562</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>37915700</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37915700</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>핏핏바디트레이닝 PT센터 구서점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>fitfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>051-512-5818</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>부산 금정구 중앙대로1873번길 14 3층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitfitness</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>213</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>193</v>
+      </c>
+      <c r="R12" t="n">
+        <v>406</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>38642628</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38642628</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>핏핏바디트레이닝 PT센터 금정본점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>fitfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>051-512-5868</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>부산 금정구 금샘로 387-1 2층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitfitness</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
         <v>214</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q13" t="n">
         <v>313</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R13" t="n">
         <v>527</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>37302400</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/37302400</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
